--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487712_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487712_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8162</v>
+        <v>6.527</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3666</v>
+        <v>2.1864</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4497</v>
+        <v>4.3407</v>
       </c>
       <c r="G2" t="n">
         <v>1.5955</v>
@@ -610,13 +610,13 @@
         <v>2.7164</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4744</v>
+        <v>1.1852</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5309</v>
+        <v>0.3507</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9435</v>
+        <v>0.8345</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>L. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0436</v>
+        <v>5.6963</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7627</v>
+        <v>2.3617</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2809</v>
+        <v>3.3346</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7854</v>
+        <v>6.3331</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9864</v>
+        <v>1.2234</v>
       </c>
       <c r="I3" t="n">
-        <v>1.799</v>
+        <v>5.1096</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7912</v>
+        <v>5.4557</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8198</v>
+        <v>0.4573</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9715</v>
+        <v>4.9984</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9941</v>
+        <v>0.8774</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1666</v>
+        <v>0.7662</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1725</v>
+        <v>0.1112</v>
       </c>
       <c r="P3" t="n">
-        <v>1.7463</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9702</v>
+        <v>-4.0747</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7164</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3582</v>
+        <v>0.3513</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0584</v>
+        <v>-0.1955</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4166</v>
+        <v>0.5468</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.8462</v>
+        <v>0.5642</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1761</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8462</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ SANCHEZ</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7927</v>
+        <v>5.4279</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5398</v>
+        <v>1.6836</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2529</v>
+        <v>3.7442</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3331</v>
+        <v>3.7854</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2234</v>
+        <v>1.9864</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1096</v>
+        <v>1.799</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4557</v>
+        <v>2.7912</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4573</v>
+        <v>0.8198</v>
       </c>
       <c r="L4" t="n">
-        <v>4.9984</v>
+        <v>1.9715</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8774</v>
+        <v>0.9941</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7662</v>
+        <v>1.1666</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1112</v>
+        <v>-0.1725</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0747</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>2.7164</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5523</v>
+        <v>0.7425</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0173</v>
+        <v>-0.1374</v>
       </c>
       <c r="U4" t="n">
-        <v>0.465</v>
+        <v>0.8799</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5642</v>
+        <v>-0.8462</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1761</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6119</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. BERMEJO FAJARDO</t>
+          <t>S. KIMOTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5897</v>
+        <v>1.3287</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9081</v>
+        <v>-0.3488</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3185</v>
+        <v>1.6774</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1537</v>
+        <v>-0.0469</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7934</v>
+        <v>-0.1631</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3603</v>
+        <v>0.1162</v>
       </c>
       <c r="J5" t="n">
-        <v>1.321</v>
+        <v>-0.2242</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6715</v>
+        <v>-0.346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6495</v>
+        <v>0.1218</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1673</v>
+        <v>0.1773</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1219</v>
+        <v>0.1829</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2892</v>
+        <v>-0.0056</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5717</v>
+        <v>0.1517</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2752</v>
+        <v>-0.1842</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2966</v>
+        <v>0.3359</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9418</v>
+        <v>1.2239</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. KIMOTO</t>
+          <t>A. FERNANDEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1101</v>
+        <v>1.0792</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6491</v>
+        <v>0.3752</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7592</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0469</v>
+        <v>0.4879</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1631</v>
+        <v>0.0297</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1162</v>
+        <v>0.4582</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2242</v>
+        <v>0.7719</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.346</v>
+        <v>0.0412</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1218</v>
+        <v>0.7307</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1773</v>
+        <v>-0.284</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1829</v>
+        <v>-0.0115</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0056</v>
+        <v>-0.2725</v>
       </c>
       <c r="P6" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.194</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.009299999999999999</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.2027</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.1642</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1642</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.0668</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.4845</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.4177</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.2239</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ SANCHEZ</t>
+          <t>F. BERMEJO FAJARDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0337</v>
+        <v>0.5792</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2751</v>
+        <v>0.7069</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.1277</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4879</v>
+        <v>1.1537</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0297</v>
+        <v>0.7934</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4582</v>
+        <v>0.3603</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7719</v>
+        <v>1.321</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0412</v>
+        <v>0.6715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7307</v>
+        <v>0.6495</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.284</v>
+        <v>-0.1673</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0115</v>
+        <v>0.1219</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2725</v>
+        <v>-0.2892</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5821</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
         <v>0.7761</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0363</v>
+        <v>0.5613</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3028</v>
+        <v>0.074</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2665</v>
+        <v>0.4873</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9418</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ESPINOSA</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0321</v>
+        <v>-0.0314</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.1737</v>
+        <v>-1.1341</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2058</v>
+        <v>1.1026</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1226</v>
+        <v>0.6049</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1303</v>
+        <v>1.3874</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2529</v>
+        <v>-0.7825</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1661</v>
+        <v>0.4443</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1813</v>
+        <v>1.071</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3474</v>
+        <v>-0.6267</v>
       </c>
       <c r="M8" t="n">
-        <v>1.0435</v>
+        <v>0.1606</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9491000000000001</v>
+        <v>0.3164</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0945</v>
+        <v>-0.1557</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1045</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9105</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3383</v>
+        <v>0.2577</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1373</v>
+        <v>-0.6082</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4756</v>
+        <v>0.8659</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9896</v>
+        <v>-0.894</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>F. ESPINOSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3862</v>
+        <v>-0.1366</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4344</v>
+        <v>-4.552</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0481</v>
+        <v>4.4154</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6049</v>
+        <v>-0.1226</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3874</v>
+        <v>1.1303</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7825</v>
+        <v>-1.2529</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4443</v>
+        <v>-1.1661</v>
       </c>
       <c r="K9" t="n">
-        <v>1.071</v>
+        <v>0.1813</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>-1.3474</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1606</v>
+        <v>1.0435</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3164</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1557</v>
+        <v>0.0945</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-3.1045</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>2.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09710000000000001</v>
+        <v>1.1695</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9085</v>
+        <v>-0.5157</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8114</v>
+        <v>1.6852</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.894</v>
+        <v>-0.9896</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4535</v>
+        <v>-0.4079</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8084</v>
+        <v>-0.7083</v>
       </c>
       <c r="F10" t="n">
-        <v>0.355</v>
+        <v>0.3005</v>
       </c>
       <c r="G10" t="n">
         <v>0.0031</v>
@@ -1234,13 +1234,13 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0969</v>
+        <v>-0.0513</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2299</v>
+        <v>-0.1298</v>
       </c>
       <c r="U10" t="n">
-        <v>0.133</v>
+        <v>0.0785</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3788</v>
+        <v>-1.2572</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.7045</v>
+        <v>-5.8826</v>
       </c>
       <c r="F11" t="n">
-        <v>4.3257</v>
+        <v>4.6255</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2168</v>
@@ -1312,13 +1312,13 @@
         <v>2.3284</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7097</v>
+        <v>0.4119</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3201</v>
+        <v>-0.4983</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="V11" t="n">
         <v>2.0701</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.1996</v>
+        <v>18.8052</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.917800000000001</v>
+        <v>-5.312</v>
       </c>
       <c r="F12" t="n">
-        <v>24.1174</v>
+        <v>24.1173</v>
       </c>
       <c r="G12" t="n">
         <v>12.5773</v>
@@ -1360,7 +1360,7 @@
         <v>9.268600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3.308699999999999</v>
+        <v>3.308700000000001</v>
       </c>
       <c r="J12" t="n">
         <v>8.0547</v>
@@ -1375,13 +1375,13 @@
         <v>4.5225</v>
       </c>
       <c r="N12" t="n">
-        <v>5.412800000000001</v>
+        <v>5.412799999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8901</v>
+        <v>-0.8901000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9702000000000002</v>
+        <v>0.9701999999999997</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.4928</v>
@@ -1390,16 +1390,16 @@
         <v>17.4628</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1835</v>
+        <v>4.789099999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6527</v>
+        <v>-2.0471</v>
       </c>
       <c r="U12" t="n">
-        <v>6.8363</v>
+        <v>6.8362</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4687000000000001</v>
+        <v>0.4686999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>5.1731</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4161</v>
+        <v>4.4979</v>
       </c>
       <c r="E13" t="n">
         <v>1.4507</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9654</v>
+        <v>3.0472</v>
       </c>
       <c r="G13" t="n">
         <v>1.7672</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1272</v>
+        <v>-0.0454</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5451</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4179</v>
+        <v>0.4997</v>
       </c>
       <c r="V13" t="n">
         <v>1.2239</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6183</v>
+        <v>2.0877</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5269</v>
+        <v>0.0264</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0913</v>
+        <v>2.0613</v>
       </c>
       <c r="G14" t="n">
         <v>1.0347</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3519</v>
+        <v>-0.1786</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4094</v>
+        <v>-0.9099</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7614</v>
+        <v>0.7313</v>
       </c>
       <c r="V14" t="n">
         <v>1.6197</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7543</v>
+        <v>1.1631</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3511</v>
+        <v>-1.7515</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1054</v>
+        <v>2.9146</v>
       </c>
       <c r="G15" t="n">
         <v>0.9360000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6243</v>
+        <v>0.0331</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3623</v>
+        <v>-0.7627</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9866</v>
+        <v>0.7958</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6459</v>
+        <v>1.1281</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.146</v>
+        <v>0.2544</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7919</v>
+        <v>0.8737</v>
       </c>
       <c r="G16" t="n">
         <v>2.297</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9033</v>
+        <v>-0.4212</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.393</v>
+        <v>-0.9926</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4897</v>
+        <v>0.5715</v>
       </c>
       <c r="V16" t="n">
         <v>-0.9418</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1569</v>
+        <v>-2.1584</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5825</v>
+        <v>-2.7652</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5744</v>
+        <v>0.6068</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7206</v>
+        <v>-2.2527</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7942</v>
+        <v>-0.2513</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9264</v>
+        <v>-2.0015</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.329</v>
+        <v>-1.2501</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6261</v>
+        <v>0.0618</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7029</v>
+        <v>-1.3118</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3916</v>
+        <v>-1.0027</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1681</v>
+        <v>-0.3131</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2235</v>
+        <v>-0.6896</v>
       </c>
       <c r="P17" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.3881</v>
+        <v>-1.5523</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3219</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1346</v>
+        <v>-0.5748</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1873</v>
+        <v>0.0017</v>
       </c>
       <c r="V17" t="n">
-        <v>0.0478</v>
+        <v>1.0555</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0478</v>
+        <v>0.4436</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5738</v>
+        <v>-2.421</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9654</v>
+        <v>-1.9829</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3916</v>
+        <v>-0.4381</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2527</v>
+        <v>-2.7206</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2513</v>
+        <v>-0.7942</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0015</v>
+        <v>-1.9264</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2501</v>
+        <v>-1.329</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0618</v>
+        <v>-0.6261</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3118</v>
+        <v>-0.7029</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0027</v>
+        <v>-1.3916</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3131</v>
+        <v>-0.1681</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6896</v>
+        <v>-1.2235</v>
       </c>
       <c r="P18" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.3881</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-1.5523</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9886</v>
+        <v>0.0578</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.775</v>
+        <v>-0.2658</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2135</v>
+        <v>0.3236</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0555</v>
+        <v>0.0478</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4436</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8939</v>
+        <v>-3.3939</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3031</v>
+        <v>-3.1029</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5908</v>
+        <v>-0.291</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6689</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6727</v>
+        <v>-0.1727</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5933</v>
+        <v>-0.3931</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0794</v>
+        <v>0.2204</v>
       </c>
       <c r="V19" t="n">
         <v>0.6119</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0134</v>
+        <v>-4.6257</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5305</v>
+        <v>-1.6306</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.4829</v>
+        <v>-2.9951</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7524999999999999</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3149</v>
+        <v>-0.9273</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4834</v>
+        <v>-0.5835</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8315</v>
+        <v>-0.3437</v>
       </c>
       <c r="V20" t="n">
         <v>-2.9459</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2446</v>
+        <v>-6.0011</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.5754</v>
+        <v>-8.9748</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3308</v>
+        <v>2.9737</v>
       </c>
       <c r="G21" t="n">
         <v>-5.9824</v>
@@ -2092,13 +2092,13 @@
         <v>2.7164</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8744</v>
+        <v>-0.6309</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.8652</v>
+        <v>-1.2646</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9909</v>
+        <v>0.6337</v>
       </c>
       <c r="V21" t="n">
         <v>1.1943</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.7515</v>
+        <v>-7.8088</v>
       </c>
       <c r="E22" t="n">
         <v>-5.0289</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7226</v>
+        <v>-2.7799</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2349</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6005</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-0.544</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0565</v>
+        <v>-0.1138</v>
       </c>
       <c r="V22" t="n">
         <v>-2.334</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-18.1995</v>
+        <v>-17.5321</v>
       </c>
       <c r="E23" t="n">
         <v>-23.5053</v>
       </c>
       <c r="F23" t="n">
-        <v>5.305699999999998</v>
+        <v>5.9732</v>
       </c>
       <c r="G23" t="n">
         <v>-12.5771</v>
@@ -2248,13 +2248,13 @@
         <v>16.4927</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.1835</v>
+        <v>-3.5161</v>
       </c>
       <c r="T23" t="n">
         <v>-6.8361</v>
       </c>
       <c r="U23" t="n">
-        <v>2.6529</v>
+        <v>3.3202</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4686000000000001</v>
